--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_単価の置き方の感度分析_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_単価の置き方の感度分析_20261005.xlsx
@@ -506,17 +506,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>年率+1.20％</t>
+          <t>年率+1.13％</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3207165</v>
+        <v>3199995</v>
       </c>
       <c r="D3" t="n">
-        <v>6256</v>
+        <v>6243</v>
       </c>
       <c r="E3" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -532,17 +532,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>年率+1.20％</t>
+          <t>年率+1.09％</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3206384</v>
+        <v>3196665</v>
       </c>
       <c r="D4" t="n">
-        <v>6255</v>
+        <v>6237</v>
       </c>
       <c r="E4" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -876,14 +876,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>価格指数の年率（令和3→令和7年度の幾何平均）　+1.205％</t>
+          <t>価格指数の年率（令和3→令和7年度の幾何平均）　+1.129％</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>報酬改定のない年の平均（令和6年度を除く）　+1.197％</t>
+          <t>報酬改定のない年の平均（令和6年度を除く）　+1.094％</t>
         </is>
       </c>
     </row>
